--- a/data/FacturasEmitidas.xlsx
+++ b/data/FacturasEmitidas.xlsx
@@ -139,31 +139,31 @@
     <t>CLI-810</t>
   </si>
   <si>
-    <t>Minera Las Bambas S.A.</t>
+    <t>Minera Altoandina S.A.C.</t>
   </si>
   <si>
     <t>Juan Carlos Pérez Gómez</t>
   </si>
   <si>
-    <t>Distribuidora Lima Norte S.A.C.</t>
+    <t>Distribuidora Vista Norte S.A.C.</t>
   </si>
   <si>
     <t>María Elena Rodríguez Prado</t>
   </si>
   <si>
-    <t>Constructora Graña &amp; Asociados</t>
+    <t>Constructora Ribera del Norte S.A.C.</t>
   </si>
   <si>
     <t>Carlos Alberto Mendoza Solís</t>
   </si>
   <si>
-    <t>Textil San Pedro E.I.R.L.</t>
+    <t>Textil Santa Aurora E.I.R.L.</t>
   </si>
   <si>
     <t>Lucía Valeria Quispe Huamán</t>
   </si>
   <si>
-    <t>Corporación Minera del Sur S.A.C.</t>
+    <t>Corporación Minera Pampa Azul S.A.C.</t>
   </si>
   <si>
     <t>Roberto Alonso Chávez Ramos</t>
